--- a/2022 data/excel_outputs/228_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/228_boothwise_data.xlsx
@@ -14,11 +14,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="537">
   <si>
     <t>AC 228 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -784,7 +850,7 @@
     <t>PRIMARY SCHOOL DHUNDHPUR ROOM NO. 02</t>
   </si>
   <si>
-    <t>UPPER PRIMARY SCHOOL (01 ■■ 08) KAITHI ROOM NO. 01</t>
+    <t>PRIMARY SCHOOL BANDA</t>
   </si>
   <si>
     <t>UPPER PRIMARY SCHOOL (01 TO 08) KAITHI ROOM NO. 02</t>
@@ -1565,8 +1631,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1582,7 +1656,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1590,12 +1664,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1894,79 +1986,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="D2" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="E2" t="s">
-        <v>497</v>
+        <v>519</v>
       </c>
       <c r="F2" t="s">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="G2" t="s">
-        <v>499</v>
+        <v>521</v>
       </c>
       <c r="H2" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="I2" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="J2" t="s">
-        <v>502</v>
+        <v>524</v>
       </c>
       <c r="K2" t="s">
-        <v>503</v>
+        <v>525</v>
       </c>
       <c r="L2" t="s">
-        <v>504</v>
+        <v>526</v>
       </c>
       <c r="M2" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="N2" t="s">
-        <v>506</v>
+        <v>528</v>
       </c>
       <c r="O2" t="s">
-        <v>507</v>
+        <v>529</v>
       </c>
       <c r="P2" t="s">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="Q2" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="R2" t="s">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="S2" t="s">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="T2" t="s">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="U2" t="s">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="V2" t="s">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="W2" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1974,7 +2132,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>903</v>
@@ -2045,7 +2203,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>937</v>
@@ -2116,7 +2274,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>873</v>
@@ -2187,7 +2345,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>503</v>
@@ -2258,7 +2416,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>696</v>
@@ -2329,7 +2487,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>730</v>
@@ -2400,7 +2558,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>409</v>
@@ -2471,7 +2629,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>1026</v>
@@ -2542,7 +2700,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>960</v>
@@ -2613,7 +2771,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>1042</v>
@@ -2684,7 +2842,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>588</v>
@@ -2755,7 +2913,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>945</v>
@@ -2826,7 +2984,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>858</v>
@@ -2897,7 +3055,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>836</v>
@@ -2968,7 +3126,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>745</v>
@@ -3039,7 +3197,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>1069</v>
@@ -3110,7 +3268,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>860</v>
@@ -3181,7 +3339,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>742</v>
@@ -3252,7 +3410,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>900</v>
@@ -3323,7 +3481,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>363</v>
@@ -3394,7 +3552,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>600</v>
@@ -3465,7 +3623,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>592</v>
@@ -3536,7 +3694,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>321</v>
@@ -3607,7 +3765,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>1084</v>
@@ -3678,7 +3836,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>1051</v>
@@ -3749,7 +3907,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>1072</v>
@@ -3820,7 +3978,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>723</v>
@@ -3891,7 +4049,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>353</v>
@@ -3962,7 +4120,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>585</v>
@@ -4033,7 +4191,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>624</v>
@@ -4104,7 +4262,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>311</v>
@@ -4175,7 +4333,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>440</v>
@@ -4246,7 +4404,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>444</v>
@@ -4317,7 +4475,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>1084</v>
@@ -4388,7 +4546,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>702</v>
@@ -4459,7 +4617,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>748</v>
@@ -4530,7 +4688,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>758</v>
@@ -4601,7 +4759,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>737</v>
@@ -4672,7 +4830,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>737</v>
@@ -4743,7 +4901,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>661</v>
@@ -4814,7 +4972,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>1070</v>
@@ -4885,7 +5043,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>969</v>
@@ -4956,7 +5114,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>1161</v>
@@ -5027,7 +5185,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>1175</v>
@@ -5098,7 +5256,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>598</v>
@@ -5169,7 +5327,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>854</v>
@@ -5240,7 +5398,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>619</v>
@@ -5311,7 +5469,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>657</v>
@@ -5382,7 +5540,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>641</v>
@@ -5453,7 +5611,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>869</v>
@@ -5524,7 +5682,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>643</v>
@@ -5595,7 +5753,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>1098</v>
@@ -5666,7 +5824,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>948</v>
@@ -5737,7 +5895,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>693</v>
@@ -5808,7 +5966,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>936</v>
@@ -5879,7 +6037,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>348</v>
@@ -5950,7 +6108,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>760</v>
@@ -6021,7 +6179,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>1111</v>
@@ -6092,7 +6250,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>962</v>
@@ -6163,7 +6321,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>521</v>
@@ -6234,7 +6392,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>933</v>
@@ -6305,7 +6463,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>718</v>
@@ -6376,7 +6534,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>973</v>
@@ -6447,7 +6605,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>793</v>
@@ -6518,7 +6676,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>1141</v>
@@ -6589,7 +6747,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>964</v>
@@ -6660,7 +6818,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>510</v>
@@ -6731,7 +6889,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>1070</v>
@@ -6802,7 +6960,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>643</v>
@@ -6873,7 +7031,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>667</v>
@@ -6944,7 +7102,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>1068</v>
@@ -7015,7 +7173,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>712</v>
@@ -7086,7 +7244,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>704</v>
@@ -7157,7 +7315,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>923</v>
@@ -7228,7 +7386,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>653</v>
@@ -7299,7 +7457,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>610</v>
@@ -7370,7 +7528,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>890</v>
@@ -7441,7 +7599,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>937</v>
@@ -7512,7 +7670,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>885</v>
@@ -7583,7 +7741,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>712</v>
@@ -7654,7 +7812,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>598</v>
@@ -7725,7 +7883,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>1078</v>
@@ -7796,7 +7954,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>1133</v>
@@ -7867,7 +8025,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>1057</v>
@@ -7938,7 +8096,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>985</v>
@@ -8009,7 +8167,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>930</v>
@@ -8080,7 +8238,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>1004</v>
@@ -8151,7 +8309,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>673</v>
@@ -8222,7 +8380,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>778</v>
@@ -8293,7 +8451,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>496</v>
@@ -8364,7 +8522,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>561</v>
@@ -8435,7 +8593,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>943</v>
@@ -8506,7 +8664,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>773</v>
@@ -8577,7 +8735,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>755</v>
@@ -8648,7 +8806,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>516</v>
@@ -8719,7 +8877,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>615</v>
@@ -8790,7 +8948,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>1097</v>
@@ -8861,7 +9019,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>836</v>
@@ -8932,7 +9090,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>757</v>
@@ -9003,7 +9161,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>1028</v>
@@ -9074,7 +9232,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C103">
         <v>774</v>
@@ -9145,7 +9303,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C104">
         <v>1125</v>
@@ -9216,7 +9374,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C105">
         <v>774</v>
@@ -9287,7 +9445,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>948</v>
@@ -9358,7 +9516,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C107">
         <v>1186</v>
@@ -9429,7 +9587,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C108">
         <v>1041</v>
@@ -9500,7 +9658,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C109">
         <v>1114</v>
@@ -9571,7 +9729,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C110">
         <v>635</v>
@@ -9642,7 +9800,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C111">
         <v>622</v>
@@ -9713,7 +9871,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C112">
         <v>1116</v>
@@ -9784,7 +9942,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C113">
         <v>1058</v>
@@ -9855,7 +10013,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>985</v>
@@ -9926,7 +10084,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>1058</v>
@@ -9997,7 +10155,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C116">
         <v>640</v>
@@ -10068,7 +10226,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>1151</v>
@@ -10139,7 +10297,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C118">
         <v>662</v>
@@ -10210,7 +10368,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C119">
         <v>762</v>
@@ -10281,7 +10439,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C120">
         <v>798</v>
@@ -10352,7 +10510,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C121">
         <v>719</v>
@@ -10423,7 +10581,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C122">
         <v>1043</v>
@@ -10494,7 +10652,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C123">
         <v>1176</v>
@@ -10565,7 +10723,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C124">
         <v>728</v>
@@ -10636,7 +10794,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C125">
         <v>623</v>
@@ -10707,7 +10865,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C126">
         <v>631</v>
@@ -10778,7 +10936,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C127">
         <v>1136</v>
@@ -10849,7 +11007,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C128">
         <v>946</v>
@@ -10920,7 +11078,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C129">
         <v>1177</v>
@@ -10991,7 +11149,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C130">
         <v>1026</v>
@@ -11062,7 +11220,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C131">
         <v>797</v>
@@ -11133,7 +11291,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C132">
         <v>651</v>
@@ -11204,7 +11362,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C133">
         <v>617</v>
@@ -11275,7 +11433,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C134">
         <v>644</v>
@@ -11346,7 +11504,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C135">
         <v>691</v>
@@ -11417,7 +11575,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C136">
         <v>441</v>
@@ -11488,7 +11646,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C137">
         <v>629</v>
@@ -11559,7 +11717,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C138">
         <v>533</v>
@@ -11630,7 +11788,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C139">
         <v>777</v>
@@ -11701,7 +11859,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C140">
         <v>497</v>
@@ -11772,7 +11930,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C141">
         <v>1051</v>
@@ -11843,7 +12001,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C142">
         <v>1001</v>
@@ -11914,7 +12072,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>567</v>
@@ -11985,7 +12143,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C144">
         <v>1048</v>
@@ -12056,7 +12214,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>927</v>
@@ -12127,7 +12285,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>1071</v>
@@ -12198,7 +12356,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>933</v>
@@ -12269,7 +12427,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>855</v>
@@ -12340,7 +12498,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>838</v>
@@ -12411,7 +12569,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>898</v>
@@ -12482,7 +12640,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>692</v>
@@ -12553,7 +12711,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>885</v>
@@ -12624,7 +12782,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>501</v>
@@ -12695,7 +12853,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>323</v>
@@ -12766,7 +12924,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>778</v>
@@ -12837,7 +12995,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>807</v>
@@ -12908,7 +13066,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>1007</v>
@@ -12979,7 +13137,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>1085</v>
@@ -13050,7 +13208,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>1145</v>
@@ -13121,7 +13279,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>682</v>
@@ -13192,7 +13350,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>681</v>
@@ -13263,7 +13421,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>591</v>
@@ -13334,7 +13492,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>488</v>
@@ -13405,7 +13563,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>563</v>
@@ -13476,7 +13634,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>735</v>
@@ -13547,7 +13705,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>776</v>
@@ -13618,7 +13776,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>785</v>
@@ -13689,7 +13847,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>752</v>
@@ -13760,7 +13918,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>812</v>
@@ -13831,7 +13989,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>1112</v>
@@ -13902,7 +14060,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>936</v>
@@ -13973,7 +14131,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>955</v>
@@ -14044,7 +14202,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>1175</v>
@@ -14115,7 +14273,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>634</v>
@@ -14186,7 +14344,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>592</v>
@@ -14257,7 +14415,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>1016</v>
@@ -14328,7 +14486,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>627</v>
@@ -14399,7 +14557,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>1027</v>
@@ -14470,7 +14628,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>967</v>
@@ -14541,7 +14699,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>1050</v>
@@ -14612,7 +14770,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>836</v>
@@ -14683,7 +14841,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>1137</v>
@@ -14754,7 +14912,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>1153</v>
@@ -14825,7 +14983,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>706</v>
@@ -14896,7 +15054,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>743</v>
@@ -14967,7 +15125,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>1142</v>
@@ -15038,7 +15196,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>1156</v>
@@ -15109,7 +15267,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>847</v>
@@ -15180,7 +15338,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>846</v>
@@ -15251,7 +15409,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>1118</v>
@@ -15322,7 +15480,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>908</v>
@@ -15393,7 +15551,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>1161</v>
@@ -15464,7 +15622,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>1104</v>
@@ -15535,7 +15693,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>1135</v>
@@ -15606,7 +15764,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>625</v>
@@ -15677,7 +15835,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>629</v>
@@ -15748,7 +15906,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>714</v>
@@ -15819,7 +15977,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>1113</v>
@@ -15890,7 +16048,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>1098</v>
@@ -15961,7 +16119,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>1086</v>
@@ -16032,7 +16190,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>684</v>
@@ -16103,7 +16261,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>676</v>
@@ -16174,7 +16332,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>719</v>
@@ -16245,7 +16403,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>688</v>
@@ -16316,7 +16474,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>869</v>
@@ -16387,7 +16545,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>586</v>
@@ -16458,7 +16616,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>1147</v>
@@ -16529,7 +16687,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>1075</v>
@@ -16600,7 +16758,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>945</v>
@@ -16671,7 +16829,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>1070</v>
@@ -16742,7 +16900,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>839</v>
@@ -16813,7 +16971,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>1082</v>
@@ -16884,7 +17042,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>988</v>
@@ -16955,7 +17113,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>724</v>
@@ -17026,7 +17184,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>730</v>
@@ -17097,7 +17255,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>502</v>
@@ -17168,7 +17326,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>671</v>
@@ -17239,7 +17397,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>1060</v>
@@ -17310,7 +17468,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>1069</v>
@@ -17381,7 +17539,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>1067</v>
@@ -17452,7 +17610,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>1034</v>
@@ -17523,7 +17681,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>658</v>
@@ -17594,7 +17752,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>625</v>
@@ -17665,7 +17823,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>1116</v>
@@ -17736,7 +17894,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>976</v>
@@ -17807,7 +17965,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>1187</v>
@@ -17878,7 +18036,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>899</v>
@@ -17949,7 +18107,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>664</v>
@@ -18020,7 +18178,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>690</v>
@@ -18091,7 +18249,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>1001</v>
@@ -18162,7 +18320,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>738</v>
@@ -18233,7 +18391,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>673</v>
@@ -18304,7 +18462,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>697</v>
@@ -18375,7 +18533,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>819</v>
@@ -18446,7 +18604,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>722</v>
@@ -18517,7 +18675,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>774</v>
@@ -18588,7 +18746,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>779</v>
@@ -18659,7 +18817,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>761</v>
@@ -18730,7 +18888,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>931</v>
@@ -18801,7 +18959,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>818</v>
@@ -18872,7 +19030,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>790</v>
@@ -18943,7 +19101,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>858</v>
@@ -19014,7 +19172,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>807</v>
@@ -19085,7 +19243,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>1161</v>
@@ -19156,7 +19314,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>1055</v>
@@ -19227,7 +19385,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>1097</v>
@@ -19298,7 +19456,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>1073</v>
@@ -19369,7 +19527,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>1021</v>
@@ -19440,7 +19598,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>355</v>
@@ -19511,7 +19669,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>872</v>
@@ -19582,7 +19740,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>849</v>
@@ -19653,7 +19811,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>820</v>
@@ -19724,7 +19882,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>769</v>
@@ -19795,7 +19953,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>1031</v>
@@ -19866,7 +20024,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>820</v>
@@ -19937,7 +20095,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>891</v>
@@ -20008,7 +20166,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>841</v>
@@ -20079,7 +20237,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>856</v>
@@ -20150,7 +20308,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>348</v>
@@ -20221,7 +20379,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>809</v>
@@ -20292,7 +20450,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C261">
         <v>1114</v>
@@ -20363,7 +20521,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C262">
         <v>1124</v>
@@ -20434,7 +20592,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C263">
         <v>734</v>
@@ -20505,7 +20663,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C264">
         <v>676</v>
@@ -20576,7 +20734,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C265">
         <v>743</v>
@@ -20647,7 +20805,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C266">
         <v>697</v>
@@ -20718,7 +20876,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C267">
         <v>1019</v>
@@ -20789,7 +20947,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C268">
         <v>340</v>
@@ -20860,7 +21018,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C269">
         <v>615</v>
@@ -20931,7 +21089,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C270">
         <v>608</v>
@@ -21002,7 +21160,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="C271">
         <v>1120</v>
@@ -21073,7 +21231,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C272">
         <v>1012</v>
@@ -21144,7 +21302,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C273">
         <v>1003</v>
@@ -21215,7 +21373,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C274">
         <v>1047</v>
@@ -21286,7 +21444,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="C275">
         <v>991</v>
@@ -21357,7 +21515,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C276">
         <v>1080</v>
@@ -21428,7 +21586,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C277">
         <v>1112</v>
@@ -21499,7 +21657,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C278">
         <v>1005</v>
@@ -21570,7 +21728,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C279">
         <v>920</v>
@@ -21641,7 +21799,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C280">
         <v>1108</v>
@@ -21712,7 +21870,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C281">
         <v>876</v>
@@ -21783,7 +21941,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C282">
         <v>796</v>
@@ -21854,7 +22012,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C283">
         <v>831</v>
@@ -21925,7 +22083,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C284">
         <v>810</v>
@@ -21996,7 +22154,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C285">
         <v>814</v>
@@ -22067,7 +22225,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="C286">
         <v>789</v>
@@ -22138,7 +22296,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C287">
         <v>779</v>
@@ -22209,7 +22367,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="C288">
         <v>813</v>
@@ -22280,7 +22438,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C289">
         <v>851</v>
@@ -22351,7 +22509,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C290">
         <v>972</v>
@@ -22422,7 +22580,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C291">
         <v>858</v>
@@ -22493,7 +22651,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="C292">
         <v>918</v>
@@ -22564,7 +22722,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C293">
         <v>908</v>
@@ -22635,7 +22793,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="C294">
         <v>866</v>
@@ -22706,7 +22864,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C295">
         <v>903</v>
@@ -22777,7 +22935,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C296">
         <v>882</v>
@@ -22848,7 +23006,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="C297">
         <v>291</v>
@@ -22919,7 +23077,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C298">
         <v>1165</v>
@@ -22990,7 +23148,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C299">
         <v>898</v>
@@ -23061,7 +23219,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C300">
         <v>795</v>
@@ -23132,7 +23290,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C301">
         <v>760</v>
@@ -23203,7 +23361,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C302">
         <v>948</v>
@@ -23274,7 +23432,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="C303">
         <v>801</v>
@@ -23345,7 +23503,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C304">
         <v>870</v>
@@ -23416,7 +23574,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C305">
         <v>918</v>
@@ -23487,7 +23645,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C306">
         <v>888</v>
@@ -23558,7 +23716,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C307">
         <v>410</v>
@@ -23629,7 +23787,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="C308">
         <v>818</v>
@@ -23700,7 +23858,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="C309">
         <v>845</v>
@@ -23771,7 +23929,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C310">
         <v>799</v>
@@ -23842,7 +24000,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C311">
         <v>1103</v>
@@ -23913,7 +24071,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="C312">
         <v>778</v>
@@ -23984,7 +24142,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="C313">
         <v>792</v>
@@ -24055,7 +24213,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C314">
         <v>1022</v>
@@ -24126,7 +24284,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="C315">
         <v>989</v>
@@ -24197,7 +24355,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C316">
         <v>999</v>
@@ -24268,7 +24426,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C317">
         <v>312</v>
@@ -24339,7 +24497,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C318">
         <v>734</v>
@@ -24410,7 +24568,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C319">
         <v>676</v>
@@ -24481,7 +24639,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C320">
         <v>845</v>
@@ -24552,7 +24710,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="C321">
         <v>796</v>
@@ -24623,7 +24781,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C322">
         <v>810</v>
@@ -24694,7 +24852,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C323">
         <v>668</v>
@@ -24765,7 +24923,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C324">
         <v>628</v>
@@ -24836,7 +24994,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C325">
         <v>574</v>
@@ -24907,7 +25065,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C326">
         <v>700</v>
@@ -24978,7 +25136,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C327">
         <v>730</v>
@@ -25049,7 +25207,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C328">
         <v>858</v>
@@ -25120,7 +25278,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C329">
         <v>853</v>
@@ -25191,7 +25349,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C330">
         <v>841</v>
@@ -25262,7 +25420,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C331">
         <v>607</v>
@@ -25333,7 +25491,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C332">
         <v>681</v>
@@ -25404,7 +25562,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C333">
         <v>833</v>
@@ -25475,7 +25633,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C334">
         <v>830</v>
@@ -25546,7 +25704,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C335">
         <v>681</v>
@@ -25617,7 +25775,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C336">
         <v>632</v>
@@ -25688,7 +25846,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C337">
         <v>359</v>
@@ -25759,7 +25917,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C338">
         <v>856</v>
@@ -25830,7 +25988,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C339">
         <v>856</v>
@@ -25901,7 +26059,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="C340">
         <v>845</v>
@@ -25972,7 +26130,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="C341">
         <v>603</v>
@@ -26043,7 +26201,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C342">
         <v>619</v>
@@ -26114,7 +26272,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C343">
         <v>1024</v>
@@ -26185,7 +26343,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C344">
         <v>708</v>
@@ -26256,7 +26414,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C345">
         <v>724</v>
@@ -26327,7 +26485,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="C346">
         <v>924</v>
@@ -26398,7 +26556,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C347">
         <v>428</v>
@@ -26469,7 +26627,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="C348">
         <v>825</v>
@@ -26540,7 +26698,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C349">
         <v>757</v>
@@ -26611,7 +26769,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C350">
         <v>1127</v>
@@ -26682,7 +26840,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="C351">
         <v>771</v>
@@ -26753,7 +26911,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C352">
         <v>1139</v>
@@ -26824,7 +26982,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C353">
         <v>1087</v>
@@ -26895,7 +27053,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C354">
         <v>387</v>
@@ -26966,7 +27124,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="C355">
         <v>736</v>
@@ -27037,7 +27195,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="C356">
         <v>699</v>
@@ -27108,7 +27266,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="C357">
         <v>860</v>
@@ -27179,7 +27337,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C358">
         <v>865</v>
@@ -27250,7 +27408,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C359">
         <v>611</v>
@@ -27321,7 +27479,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="C360">
         <v>257</v>
@@ -27392,7 +27550,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="C361">
         <v>517</v>
@@ -27463,7 +27621,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C362">
         <v>1081</v>
@@ -27534,7 +27692,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C363">
         <v>1038</v>
@@ -27605,7 +27763,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C364">
         <v>906</v>
@@ -27676,7 +27834,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="C365">
         <v>918</v>
@@ -27747,7 +27905,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="C366">
         <v>894</v>
@@ -27818,7 +27976,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C367">
         <v>1086</v>
@@ -27889,7 +28047,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="C368">
         <v>965</v>
@@ -27960,7 +28118,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="C369">
         <v>1097</v>
@@ -28031,7 +28189,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="C370">
         <v>1035</v>
@@ -28102,7 +28260,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="C371">
         <v>931</v>
@@ -28173,7 +28331,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="C372">
         <v>844</v>
@@ -28244,7 +28402,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="C373">
         <v>642</v>
@@ -28315,7 +28473,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="C374">
         <v>649</v>
@@ -28386,7 +28544,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="C375">
         <v>882</v>
@@ -28457,7 +28615,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="C376">
         <v>710</v>
@@ -28528,7 +28686,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="C377">
         <v>718</v>
@@ -28599,7 +28757,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="C378">
         <v>1137</v>
@@ -28670,7 +28828,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="C379">
         <v>583</v>
@@ -28741,7 +28899,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="C380">
         <v>631</v>
@@ -28812,7 +28970,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="C381">
         <v>1047</v>
@@ -28883,7 +29041,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="C382">
         <v>721</v>
@@ -28954,7 +29112,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="C383">
         <v>849</v>
@@ -29025,7 +29183,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="C384">
         <v>761</v>
@@ -29096,7 +29254,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="C385">
         <v>814</v>
@@ -29167,7 +29325,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="C386">
         <v>663</v>
@@ -29238,7 +29396,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="C387">
         <v>767</v>
@@ -29309,7 +29467,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="C388">
         <v>1221</v>
@@ -29380,7 +29538,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="C389">
         <v>1038</v>
@@ -29451,7 +29609,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="C390">
         <v>1185</v>
@@ -29522,7 +29680,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="C391">
         <v>613</v>
@@ -29593,7 +29751,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C392">
         <v>619</v>
@@ -29664,7 +29822,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C393">
         <v>1117</v>
@@ -29735,7 +29893,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="C394">
         <v>1126</v>
@@ -29806,7 +29964,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="C395">
         <v>884</v>
@@ -29877,7 +30035,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="C396">
         <v>753</v>
@@ -29948,7 +30106,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C397">
         <v>702</v>
@@ -30019,7 +30177,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="C398">
         <v>791</v>
@@ -30090,7 +30248,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="C399">
         <v>920</v>
@@ -30161,7 +30319,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="C400">
         <v>876</v>
@@ -30232,7 +30390,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="C401">
         <v>964</v>
@@ -30303,7 +30461,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="C402">
         <v>845</v>
@@ -30374,7 +30532,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="C403">
         <v>841</v>
@@ -30445,7 +30603,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="C404">
         <v>1023</v>
@@ -30516,7 +30674,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="C405">
         <v>977</v>
@@ -30587,7 +30745,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="C406">
         <v>996</v>
@@ -30658,7 +30816,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="C407">
         <v>1114</v>
@@ -30729,7 +30887,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="C408">
         <v>984</v>
@@ -30800,7 +30958,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C409">
         <v>1039</v>
@@ -30871,7 +31029,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="C410">
         <v>847</v>
@@ -30942,7 +31100,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="C411">
         <v>936</v>
@@ -31013,7 +31171,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="C412">
         <v>882</v>
@@ -31084,7 +31242,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="C413">
         <v>1037</v>
@@ -31155,7 +31313,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="C414">
         <v>1131</v>
@@ -31226,7 +31384,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="C415">
         <v>1065</v>
@@ -31297,7 +31455,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="C416">
         <v>640</v>
@@ -31368,7 +31526,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="C417">
         <v>827</v>
@@ -31439,7 +31597,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="C418">
         <v>796</v>
@@ -31510,7 +31668,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="C419">
         <v>865</v>
@@ -31581,7 +31739,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="C420">
         <v>690</v>
@@ -31652,7 +31810,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="C421">
         <v>1162</v>
@@ -31723,7 +31881,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="C422">
         <v>779</v>
@@ -31794,7 +31952,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="C423">
         <v>831</v>
@@ -31865,7 +32023,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C424">
         <v>637</v>
@@ -31936,7 +32094,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="C425">
         <v>690</v>
@@ -32007,7 +32165,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="C426">
         <v>642</v>
@@ -32078,7 +32236,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="C427">
         <v>911</v>
@@ -32149,7 +32307,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="C428">
         <v>911</v>
@@ -32220,7 +32378,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="C429">
         <v>852</v>
@@ -32291,7 +32449,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="C430">
         <v>622</v>
@@ -32362,7 +32520,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="C431">
         <v>753</v>
@@ -32433,7 +32591,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="C432">
         <v>937</v>
@@ -32504,7 +32662,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="C433">
         <v>829</v>
@@ -32575,7 +32733,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="C434">
         <v>859</v>
@@ -32646,7 +32804,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="C435">
         <v>761</v>
@@ -32717,7 +32875,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="C436">
         <v>910</v>
@@ -32788,7 +32946,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="C437">
         <v>766</v>
@@ -32859,7 +33017,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="C438">
         <v>795</v>
@@ -32930,7 +33088,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="C439">
         <v>792</v>
@@ -33001,7 +33159,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="C440">
         <v>800</v>
@@ -33072,7 +33230,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="C441">
         <v>511</v>
@@ -33143,7 +33301,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="C442">
         <v>926</v>
@@ -33214,7 +33372,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="C443">
         <v>667</v>
@@ -33285,7 +33443,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="C444">
         <v>679</v>
@@ -33356,7 +33514,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="C445">
         <v>1049</v>
@@ -33427,7 +33585,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="C446">
         <v>1031</v>
@@ -33498,7 +33656,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="C447">
         <v>1084</v>
@@ -33569,7 +33727,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="C448">
         <v>948</v>
@@ -33640,7 +33798,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>447</v>
+        <v>469</v>
       </c>
       <c r="C449">
         <v>628</v>
@@ -33711,7 +33869,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="C450">
         <v>686</v>
@@ -33782,7 +33940,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="C451">
         <v>666</v>
@@ -33853,7 +34011,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="C452">
         <v>1042</v>
@@ -33924,7 +34082,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="C453">
         <v>933</v>
@@ -33995,7 +34153,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="C454">
         <v>985</v>
@@ -34066,7 +34224,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="C455">
         <v>880</v>
@@ -34137,7 +34295,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="C456">
         <v>977</v>
@@ -34208,7 +34366,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="C457">
         <v>1106</v>
@@ -34279,7 +34437,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="C458">
         <v>560</v>
@@ -34350,7 +34508,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="C459">
         <v>628</v>
@@ -34421,7 +34579,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="C460">
         <v>804</v>
@@ -34492,7 +34650,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="C461">
         <v>725</v>
@@ -34563,7 +34721,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="C462">
         <v>1043</v>
@@ -34634,7 +34792,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="C463">
         <v>856</v>
@@ -34705,7 +34863,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="C464">
         <v>775</v>
@@ -34776,7 +34934,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="C465">
         <v>864</v>
@@ -34847,7 +35005,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="C466">
         <v>860</v>
@@ -34918,7 +35076,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="C467">
         <v>816</v>
@@ -34989,7 +35147,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="C468">
         <v>814</v>
@@ -35060,7 +35218,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="C469">
         <v>795</v>
@@ -35131,7 +35289,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C470">
         <v>791</v>
@@ -35202,7 +35360,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="C471">
         <v>795</v>
@@ -35273,7 +35431,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="C472">
         <v>746</v>
@@ -35344,7 +35502,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="C473">
         <v>628</v>
@@ -35415,7 +35573,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="C474">
         <v>603</v>
@@ -35486,7 +35644,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="C475">
         <v>681</v>
@@ -35557,7 +35715,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="C476">
         <v>799</v>
@@ -35628,7 +35786,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="C477">
         <v>1037</v>
@@ -35699,7 +35857,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="C478">
         <v>894</v>
@@ -35770,7 +35928,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="C479">
         <v>672</v>
@@ -35841,7 +35999,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="C480">
         <v>649</v>
@@ -35912,7 +36070,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C481">
         <v>882</v>
@@ -35983,7 +36141,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="C482">
         <v>768</v>
@@ -36054,7 +36212,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="C483">
         <v>711</v>
@@ -36125,7 +36283,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="s">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="C484">
         <v>776</v>
@@ -36196,7 +36354,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
       <c r="C485">
         <v>853</v>
@@ -36267,7 +36425,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="s">
-        <v>484</v>
+        <v>506</v>
       </c>
       <c r="C486">
         <v>761</v>
@@ -36338,7 +36496,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="s">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="C487">
         <v>1034</v>
@@ -36409,7 +36567,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="s">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="C488">
         <v>770</v>
@@ -36480,7 +36638,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="s">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="C489">
         <v>1006</v>
@@ -36551,7 +36709,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="s">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="C490">
         <v>1036</v>
@@ -36622,7 +36780,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="s">
-        <v>489</v>
+        <v>511</v>
       </c>
       <c r="C491">
         <v>987</v>
@@ -36693,7 +36851,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="s">
-        <v>490</v>
+        <v>512</v>
       </c>
       <c r="C492">
         <v>963</v>
@@ -36764,7 +36922,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="s">
-        <v>491</v>
+        <v>513</v>
       </c>
       <c r="C493">
         <v>983</v>
@@ -36835,7 +36993,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="C494">
         <v>1077</v>
@@ -36906,7 +37064,7 @@
         <v>493</v>
       </c>
       <c r="B495" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="C495">
         <v>1063</v>
@@ -36977,7 +37135,7 @@
         <v>494</v>
       </c>
       <c r="B496" t="s">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="C496">
         <v>496</v>
